--- a/public/templates/forms/A-044-DataRetentionSchedule-FORM.xlsx
+++ b/public/templates/forms/A-044-DataRetentionSchedule-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="13">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -325,7 +325,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -359,7 +359,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-044-DataRetentionSchedule-FORM.xlsx
+++ b/public/templates/forms/A-044-DataRetentionSchedule-FORM.xlsx
@@ -4,20 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Form!$16:$16</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="13">
     <font>
       <name val="Aptos"/>
@@ -151,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -205,6 +210,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -569,7 +577,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -694,7 +702,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
           <t>This schedule maps each category of data the Agency holds to its retention period and the basis for that period, and authorizes disposal at end of period. It takes its categories and classification levels from the Data Classification Policy and the Data Inventory / Data Map, and drives the Secure Disposal Procedures.</t>
@@ -729,7 +737,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Data Category</t>
@@ -1078,7 +1086,7 @@
       <c r="C52" s="10" t="inlineStr"/>
       <c r="D52" s="10" t="inlineStr"/>
     </row>
-    <row r="54" ht="70" customHeight="1">
+    <row r="54" ht="82.2" customHeight="1">
       <c r="A54" s="14" t="inlineStr">
         <is>
           <t>Drafter's note (internal, delete before publishing): Recast from the Schedule type to a Reference Matrix per the approved batch review: the cadence columns (frequency / next due / last completed) did not model retention rules. A sign-off block was ported in from the Schedule shell because a retention schedule carries legal weight and authorizes disposal. Owner and Next Review are per-row (records custody differs by category); the header Owner is the overall custodian. NENA citations map to §4.1.4.1 (classification policy covering retention and disposal of records and data), §4.2.2.5 (destruction / disposal procedures), §4.2.5 (retention of public-records-request documentation), and §6.24 (Disposal). Indiana authority resolved to IC 5-15-6 (Local Public Records Commissions); the adopting PSAP applies the IARA County/Local Retention Schedule periods, which set the floor for the per-category minimums in the grid.</t>
@@ -1135,7 +1143,8 @@
       <formula1>"Internal,Restricted,Confidential"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1143,7 +1152,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1190,7 +1199,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="34.7" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Data Category</t>
@@ -1212,7 +1221,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="34.7" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Classification</t>
@@ -1278,7 +1287,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Regulatory / Operational Basis</t>
@@ -1300,7 +1309,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Disposition Trigger</t>
@@ -1322,7 +1331,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1360,10 +1369,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>2027-01-01</t>
-        </is>
+      <c r="D12" s="22">
+        <v>46388</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
@@ -1439,6 +1446,7 @@
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="B19:D19"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>